--- a/BoardGame_Excel/BoardGame_250703.xlsx
+++ b/BoardGame_Excel/BoardGame_250703.xlsx
@@ -2142,10 +2142,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>문양이 같은 카드 3장과, 2장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ex) 3 Spade &amp; 2 Club</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2380,6 +2376,10 @@
    - 특수효과 룬 관련 UI 추가 (365행)
 ㅁ카드 시트 수정
    - 특수효과에 대한 내용 수정 (87행)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숫자가 같은 카드 3장과, 2장</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5075,7 +5075,7 @@
         <v>544</v>
       </c>
       <c r="D11" s="37" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="O11" t="s">
         <v>298</v>
@@ -5092,10 +5092,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="15" spans="2:83" x14ac:dyDescent="0.3">
@@ -6661,17 +6661,17 @@
     <row r="192" spans="3:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="C192" s="51"/>
       <c r="D192" s="8" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="193" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E193" s="27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="194" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E194" s="27" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="195" spans="5:5" x14ac:dyDescent="0.3">
@@ -7707,53 +7707,53 @@
     <row r="365" spans="4:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D365" s="51"/>
       <c r="E365" s="8" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="379" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E379" s="9" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="380" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E380" s="9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="381" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E381" s="9" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="382" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E382" s="54" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="383" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E383" s="9" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="384" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E384" s="54" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="385" spans="4:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D385" s="51"/>
       <c r="E385" s="8" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="386" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E386" s="9" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="406" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E406" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
   </sheetData>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="D6" s="5"/>
       <c r="F6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="20.25" x14ac:dyDescent="0.3">
@@ -8380,7 +8380,7 @@
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C45" s="41">
         <v>25</v>
@@ -8401,7 +8401,7 @@
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C46" s="41">
         <v>26</v>
@@ -8422,7 +8422,7 @@
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C47" s="41">
         <v>27</v>
@@ -8443,7 +8443,7 @@
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C48" s="41">
         <v>28</v>
@@ -9004,7 +9004,7 @@
         <v>201</v>
       </c>
       <c r="H76" s="50" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.3">
@@ -9024,7 +9024,7 @@
         <v>202</v>
       </c>
       <c r="H77" s="39" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.3">
@@ -9044,7 +9044,7 @@
         <v>203</v>
       </c>
       <c r="H78" s="39" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.3">
@@ -9064,7 +9064,7 @@
         <v>205</v>
       </c>
       <c r="H79" s="39" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.3">
@@ -9084,7 +9084,7 @@
         <v>206</v>
       </c>
       <c r="H80" s="39" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
@@ -9104,7 +9104,7 @@
         <v>542</v>
       </c>
       <c r="H81" s="39" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
@@ -9121,10 +9121,10 @@
         <v>100</v>
       </c>
       <c r="G82" s="39" t="s">
+        <v>598</v>
+      </c>
+      <c r="H82" s="39" t="s">
         <v>549</v>
-      </c>
-      <c r="H82" s="39" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
@@ -9161,7 +9161,7 @@
         <v>500</v>
       </c>
       <c r="G84" s="39" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H84" s="39" t="s">
         <v>546</v>
@@ -9190,47 +9190,47 @@
     <row r="87" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A87" s="51"/>
       <c r="D87" s="8" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D88" s="27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D89" s="27" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D90" s="27" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D91" s="27" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D92" s="27" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D93" s="27" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D94" s="27" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D95" s="27" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
@@ -9244,13 +9244,13 @@
         <v>301</v>
       </c>
       <c r="F96" s="42" t="s">
+        <v>560</v>
+      </c>
+      <c r="G96" s="42" t="s">
         <v>561</v>
       </c>
-      <c r="G96" s="42" t="s">
-        <v>562</v>
-      </c>
       <c r="H96" s="42" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="I96" s="42" t="s">
         <v>190</v>
@@ -9271,13 +9271,13 @@
         <v>538</v>
       </c>
       <c r="G97" s="53" t="s">
+        <v>572</v>
+      </c>
+      <c r="H97" s="53" t="s">
+        <v>569</v>
+      </c>
+      <c r="I97" s="49" t="s">
         <v>573</v>
-      </c>
-      <c r="H97" s="53" t="s">
-        <v>570</v>
-      </c>
-      <c r="I97" s="49" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -9294,13 +9294,13 @@
         <v>539</v>
       </c>
       <c r="G98" s="53" t="s">
+        <v>574</v>
+      </c>
+      <c r="H98" s="53" t="s">
+        <v>570</v>
+      </c>
+      <c r="I98" s="50" t="s">
         <v>575</v>
-      </c>
-      <c r="H98" s="53" t="s">
-        <v>571</v>
-      </c>
-      <c r="I98" s="50" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -9317,13 +9317,13 @@
         <v>540</v>
       </c>
       <c r="G99" s="53" t="s">
+        <v>579</v>
+      </c>
+      <c r="H99" s="53" t="s">
+        <v>571</v>
+      </c>
+      <c r="I99" s="50" t="s">
         <v>580</v>
-      </c>
-      <c r="H99" s="53" t="s">
-        <v>572</v>
-      </c>
-      <c r="I99" s="50" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -9340,13 +9340,13 @@
         <v>541</v>
       </c>
       <c r="G100" s="53" t="s">
+        <v>576</v>
+      </c>
+      <c r="H100" s="53" t="s">
+        <v>568</v>
+      </c>
+      <c r="I100" s="53" t="s">
         <v>577</v>
-      </c>
-      <c r="H100" s="53" t="s">
-        <v>569</v>
-      </c>
-      <c r="I100" s="53" t="s">
-        <v>578</v>
       </c>
     </row>
   </sheetData>

--- a/BoardGame_Excel/BoardGame_250703.xlsx
+++ b/BoardGame_Excel/BoardGame_250703.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="History" sheetId="1" r:id="rId1"/>

--- a/BoardGame_Excel/BoardGame_250703.xlsx
+++ b/BoardGame_Excel/BoardGame_250703.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="History" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="601">
   <si>
     <t>작성자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -217,11 +217,6 @@
   </si>
   <si>
     <t>몬스터 체력 10% 회복</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2048 미니게임 시작
-최종 숫자만큼 데미지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2380,6 +2375,20 @@
   </si>
   <si>
     <t>숫자가 같은 카드 3장과, 2장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2048 미니게임 시작
+최종 숫자만큼 데미지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버프: 데미지 2배, 턴 +1
+디버프: 데미지 1/2, 턴 -1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유저 체력 10% 회복</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4978,7 +4987,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="2:83" x14ac:dyDescent="0.3">
@@ -4986,10 +4995,10 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="2:83" x14ac:dyDescent="0.3">
@@ -4997,10 +5006,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="2:83" ht="49.5" x14ac:dyDescent="0.3">
@@ -5008,13 +5017,13 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="CE6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="2:83" ht="33" x14ac:dyDescent="0.3">
@@ -5022,10 +5031,10 @@
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8" spans="2:83" x14ac:dyDescent="0.3">
@@ -5033,10 +5042,10 @@
         <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D8" s="37" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9" spans="2:83" ht="49.5" x14ac:dyDescent="0.3">
@@ -5044,10 +5053,10 @@
         <v>3</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="10" spans="2:83" ht="132" x14ac:dyDescent="0.3">
@@ -5055,16 +5064,16 @@
         <v>3</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="O10" t="s">
+        <v>295</v>
+      </c>
+      <c r="P10" t="s">
         <v>296</v>
-      </c>
-      <c r="P10" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="11" spans="2:83" ht="33" x14ac:dyDescent="0.3">
@@ -5072,19 +5081,19 @@
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D11" s="37" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="O11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q11" t="s">
+        <v>295</v>
+      </c>
+      <c r="R11" t="s">
         <v>296</v>
-      </c>
-      <c r="R11" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="12" spans="2:83" ht="99" x14ac:dyDescent="0.3">
@@ -5092,20 +5101,20 @@
         <v>3</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="15" spans="2:83" x14ac:dyDescent="0.3">
       <c r="K15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -5131,7 +5140,7 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
@@ -5216,77 +5225,77 @@
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" s="8"/>
       <c r="D16" s="27" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E16" s="22"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="8"/>
       <c r="D17" s="27" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E17" s="22"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="8"/>
       <c r="D18" s="27" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E18" s="22"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="8"/>
       <c r="D19" s="27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E19" s="22"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="8"/>
       <c r="D20" s="27" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E20" s="22"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="8"/>
       <c r="D21" s="27" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E21" s="22"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="8"/>
       <c r="D22" s="27" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E22" s="22"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="8"/>
       <c r="D23" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E23" s="22"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="8"/>
       <c r="D24" s="27" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E24" s="22"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="8"/>
       <c r="D25" s="27" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E25" s="22"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="8"/>
       <c r="C26" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D26" s="27"/>
       <c r="E26" s="22"/>
@@ -5294,7 +5303,7 @@
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="8"/>
       <c r="D27" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E27" s="22"/>
     </row>
@@ -5302,13 +5311,13 @@
       <c r="B28" s="8"/>
       <c r="D28" s="8"/>
       <c r="E28" s="22" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="8"/>
       <c r="D29" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E29" s="22"/>
     </row>
@@ -5316,27 +5325,27 @@
       <c r="B30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="8"/>
       <c r="D33" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E33" s="22"/>
     </row>
@@ -5344,41 +5353,41 @@
       <c r="B34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="22" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="8"/>
       <c r="D35" s="8"/>
       <c r="E35" s="22" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="8"/>
       <c r="D38" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E38" s="22"/>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" s="8"/>
       <c r="D39" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E39" s="8"/>
     </row>
@@ -5386,120 +5395,120 @@
       <c r="B40" s="8"/>
       <c r="D40" s="8"/>
       <c r="E40" s="22" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D41" s="8"/>
       <c r="E41" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E42" s="22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D43" s="8"/>
       <c r="E43" s="22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D44" s="8"/>
       <c r="E44" s="35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D45" s="8"/>
       <c r="E45" s="22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D46" s="8"/>
       <c r="E46" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D47" s="8"/>
       <c r="E47" s="17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D48" s="8"/>
       <c r="E48" s="34" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="49" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D49" s="8"/>
       <c r="E49" s="35" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="50" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D50" s="8"/>
       <c r="E50" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="51" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D51" s="8"/>
       <c r="E51" s="34" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="52" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D52" s="8"/>
       <c r="E52" s="17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="53" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D53" s="8"/>
       <c r="E53" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="54" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D54" s="8"/>
       <c r="E54" s="17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="55" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D55" s="8"/>
       <c r="E55" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="56" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D56" s="8"/>
       <c r="E56" s="34" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="57" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D57" s="8"/>
       <c r="E57" s="17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="58" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D58" s="8"/>
       <c r="E58" s="17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="59" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D59" s="8"/>
       <c r="E59" s="17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="60" spans="4:5" x14ac:dyDescent="0.3">
@@ -5514,12 +5523,12 @@
     </row>
     <row r="68" spans="4:10" x14ac:dyDescent="0.3">
       <c r="E68" s="22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="69" spans="4:10" x14ac:dyDescent="0.3">
       <c r="E69" s="22" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="70" spans="4:10" x14ac:dyDescent="0.3">
@@ -5556,7 +5565,7 @@
         <v>26</v>
       </c>
       <c r="H74" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I74" s="14" t="s">
         <v>27</v>
@@ -5575,7 +5584,7 @@
         <v>1</v>
       </c>
       <c r="H75" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I75" s="15" t="s">
         <v>37</v>
@@ -5594,7 +5603,7 @@
         <v>34</v>
       </c>
       <c r="H76" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I76" s="15" t="s">
         <v>38</v>
@@ -5613,7 +5622,7 @@
         <v>35</v>
       </c>
       <c r="H77" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I77" s="15" t="s">
         <v>39</v>
@@ -5632,10 +5641,10 @@
         <v>5</v>
       </c>
       <c r="H78" s="13" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I78" s="15" t="s">
-        <v>42</v>
+        <v>600</v>
       </c>
       <c r="J78" s="9"/>
     </row>
@@ -5651,14 +5660,14 @@
         <v>13</v>
       </c>
       <c r="H79" s="13" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I79" s="15" t="s">
         <v>43</v>
       </c>
       <c r="J79" s="9"/>
     </row>
-    <row r="80" spans="4:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="4:10" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D80" s="29">
         <v>5</v>
       </c>
@@ -5670,14 +5679,14 @@
         <v>9</v>
       </c>
       <c r="H80" s="13" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I80" s="16" t="s">
-        <v>41</v>
+        <v>599</v>
       </c>
       <c r="J80" s="9"/>
     </row>
-    <row r="81" spans="4:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="4:10" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D81" s="29">
         <v>6</v>
       </c>
@@ -5689,10 +5698,10 @@
         <v>36</v>
       </c>
       <c r="H81" s="13" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I81" s="16" t="s">
-        <v>44</v>
+        <v>598</v>
       </c>
       <c r="J81" s="9"/>
     </row>
@@ -5704,19 +5713,19 @@
     </row>
     <row r="83" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D83" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E83" s="22"/>
     </row>
     <row r="84" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D84" s="8"/>
       <c r="E84" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="85" spans="4:10" x14ac:dyDescent="0.3">
       <c r="E85" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="86" spans="4:10" x14ac:dyDescent="0.3">
@@ -5736,79 +5745,79 @@
     </row>
     <row r="98" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E98" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="99" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E99" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J99" s="9"/>
     </row>
     <row r="100" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E100" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J100" s="9"/>
     </row>
     <row r="101" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E101" s="22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J101" s="9"/>
     </row>
     <row r="102" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E102" s="22" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J102" s="9"/>
     </row>
     <row r="103" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E103" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J103" s="9"/>
     </row>
     <row r="104" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E104" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J104" s="22"/>
     </row>
     <row r="105" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E105" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J105" s="9"/>
     </row>
     <row r="106" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E106" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="107" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E107" s="22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="108" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E108" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="109" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E109" s="22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="110" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E110" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="111" spans="5:10" x14ac:dyDescent="0.3">
       <c r="E111" s="17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="112" spans="5:10" x14ac:dyDescent="0.3">
@@ -5819,7 +5828,7 @@
         <v>24</v>
       </c>
       <c r="G112" s="33" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H112" s="33" t="s">
         <v>27</v>
@@ -5830,13 +5839,13 @@
         <v>0</v>
       </c>
       <c r="F113" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H113" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="114" spans="5:8" x14ac:dyDescent="0.3">
@@ -5844,13 +5853,13 @@
         <v>1</v>
       </c>
       <c r="F114" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H114" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="115" spans="5:8" x14ac:dyDescent="0.3">
@@ -5858,13 +5867,13 @@
         <v>2</v>
       </c>
       <c r="F115" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H115" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="116" spans="5:8" x14ac:dyDescent="0.3">
@@ -5872,13 +5881,13 @@
         <v>3</v>
       </c>
       <c r="F116" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H116" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="117" spans="5:8" x14ac:dyDescent="0.3">
@@ -5886,18 +5895,18 @@
         <v>4</v>
       </c>
       <c r="F117" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H117" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="118" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E118" s="17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="119" spans="5:8" x14ac:dyDescent="0.3">
@@ -5908,7 +5917,7 @@
         <v>24</v>
       </c>
       <c r="G119" s="33" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="120" spans="5:8" x14ac:dyDescent="0.3">
@@ -5935,7 +5944,7 @@
     </row>
     <row r="122" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E122" s="17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="123" spans="5:8" x14ac:dyDescent="0.3">
@@ -5946,7 +5955,7 @@
         <v>24</v>
       </c>
       <c r="G123" s="33" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="124" spans="5:8" x14ac:dyDescent="0.3">
@@ -5954,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="F124" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G124" s="36">
         <v>0.6</v>
@@ -5965,7 +5974,7 @@
         <v>1</v>
       </c>
       <c r="F125" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G125" s="36">
         <v>0.3</v>
@@ -5976,7 +5985,7 @@
         <v>2</v>
       </c>
       <c r="F126" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G126" s="36">
         <v>0.1</v>
@@ -5984,7 +5993,7 @@
     </row>
     <row r="127" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E127" s="17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="128" spans="5:8" x14ac:dyDescent="0.3">
@@ -5992,10 +6001,10 @@
         <v>23</v>
       </c>
       <c r="F128" s="33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G128" s="33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="129" spans="3:9" x14ac:dyDescent="0.3">
@@ -6009,27 +6018,27 @@
     </row>
     <row r="130" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D130" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="131" spans="3:9" x14ac:dyDescent="0.3">
       <c r="E131" s="22" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="132" spans="3:9" x14ac:dyDescent="0.3">
       <c r="E132" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="133" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="C133" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="134" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D134" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="135" spans="3:9" x14ac:dyDescent="0.3">
@@ -6040,13 +6049,13 @@
         <v>24</v>
       </c>
       <c r="G135" s="33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H135" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I135" s="33" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="136" spans="3:9" x14ac:dyDescent="0.3">
@@ -6054,7 +6063,7 @@
         <v>0</v>
       </c>
       <c r="F136" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G136" s="2">
         <v>5</v>
@@ -6071,7 +6080,7 @@
         <v>1</v>
       </c>
       <c r="F137" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G137" s="2">
         <v>6</v>
@@ -6088,7 +6097,7 @@
         <v>2</v>
       </c>
       <c r="F138" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G138" s="2">
         <v>7</v>
@@ -6105,7 +6114,7 @@
         <v>3</v>
       </c>
       <c r="F139" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G139" s="2">
         <v>8</v>
@@ -6122,7 +6131,7 @@
         <v>4</v>
       </c>
       <c r="F140" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G140" s="2">
         <v>9</v>
@@ -6136,7 +6145,7 @@
     </row>
     <row r="142" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D142" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="143" spans="3:9" x14ac:dyDescent="0.3">
@@ -6147,13 +6156,13 @@
         <v>24</v>
       </c>
       <c r="G143" s="33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H143" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I143" s="33" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="144" spans="3:9" x14ac:dyDescent="0.3">
@@ -6161,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="F144" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G144" s="2">
         <v>10</v>
@@ -6178,7 +6187,7 @@
         <v>1</v>
       </c>
       <c r="F145" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G145" s="2">
         <v>11</v>
@@ -6195,7 +6204,7 @@
         <v>2</v>
       </c>
       <c r="F146" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G146" s="2">
         <v>10</v>
@@ -6212,7 +6221,7 @@
         <v>3</v>
       </c>
       <c r="F147" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G147" s="2">
         <v>12</v>
@@ -6229,7 +6238,7 @@
         <v>4</v>
       </c>
       <c r="F148" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G148" s="2">
         <v>15</v>
@@ -6243,7 +6252,7 @@
     </row>
     <row r="150" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D150" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="151" spans="3:9" x14ac:dyDescent="0.3">
@@ -6254,13 +6263,13 @@
         <v>24</v>
       </c>
       <c r="G151" s="33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H151" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I151" s="33" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="152" spans="3:9" x14ac:dyDescent="0.3">
@@ -6268,7 +6277,7 @@
         <v>0</v>
       </c>
       <c r="F152" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G152" s="2">
         <v>15</v>
@@ -6285,7 +6294,7 @@
         <v>1</v>
       </c>
       <c r="F153" s="13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G153" s="2">
         <v>15</v>
@@ -6302,7 +6311,7 @@
         <v>2</v>
       </c>
       <c r="F154" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G154" s="2">
         <v>15</v>
@@ -6319,7 +6328,7 @@
         <v>3</v>
       </c>
       <c r="F155" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G155" s="2">
         <v>15</v>
@@ -6336,7 +6345,7 @@
         <v>4</v>
       </c>
       <c r="F156" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G156" s="2">
         <v>20</v>
@@ -6350,7 +6359,7 @@
     </row>
     <row r="157" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="C157" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="158" spans="3:9" x14ac:dyDescent="0.3">
@@ -6361,13 +6370,13 @@
         <v>24</v>
       </c>
       <c r="G158" s="33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H158" s="33" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I158" s="33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="159" spans="3:9" x14ac:dyDescent="0.3">
@@ -6375,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="F159" s="13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G159" s="2">
         <v>100</v>
@@ -6387,7 +6396,7 @@
     </row>
     <row r="161" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="C161" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D161" s="22"/>
       <c r="E161"/>
@@ -6395,7 +6404,7 @@
     <row r="162" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="C162" s="26"/>
       <c r="D162" s="22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E162"/>
     </row>
@@ -6408,13 +6417,13 @@
         <v>24</v>
       </c>
       <c r="G163" s="33" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H163" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="I163" s="33" t="s">
         <v>189</v>
-      </c>
-      <c r="I163" s="33" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="164" spans="3:9" ht="17.25" x14ac:dyDescent="0.3">
@@ -6423,13 +6432,13 @@
         <v>0</v>
       </c>
       <c r="F164" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G164" s="13">
         <v>5</v>
       </c>
       <c r="H164" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I164" s="13"/>
     </row>
@@ -6439,13 +6448,13 @@
         <v>1</v>
       </c>
       <c r="F165" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G165" s="13">
         <v>10</v>
       </c>
       <c r="H165" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I165" s="13"/>
     </row>
@@ -6455,13 +6464,13 @@
         <v>2</v>
       </c>
       <c r="F166" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G166" s="13">
         <v>20</v>
       </c>
       <c r="H166" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I166" s="13"/>
     </row>
@@ -6471,13 +6480,13 @@
         <v>3</v>
       </c>
       <c r="F167" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G167" s="13">
         <v>40</v>
       </c>
       <c r="H167" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I167" s="13"/>
     </row>
@@ -6487,13 +6496,13 @@
         <v>4</v>
       </c>
       <c r="F168" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G168" s="13">
         <v>200</v>
       </c>
       <c r="H168" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I168" s="13"/>
     </row>
@@ -6503,13 +6512,13 @@
         <v>5</v>
       </c>
       <c r="F169" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G169" s="13">
         <v>80</v>
       </c>
       <c r="H169" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I169" s="13"/>
     </row>
@@ -6519,13 +6528,13 @@
         <v>6</v>
       </c>
       <c r="F170" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G170" s="13">
         <v>100</v>
       </c>
       <c r="H170" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I170" s="13"/>
     </row>
@@ -6535,13 +6544,13 @@
         <v>7</v>
       </c>
       <c r="F171" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G171" s="13">
         <v>300</v>
       </c>
       <c r="H171" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I171" s="13"/>
     </row>
@@ -6551,13 +6560,13 @@
         <v>8</v>
       </c>
       <c r="F172" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G172" s="13">
         <v>500</v>
       </c>
       <c r="H172" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I172" s="13"/>
     </row>
@@ -6567,111 +6576,111 @@
         <v>9</v>
       </c>
       <c r="F173" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G173" s="13">
         <v>1000</v>
       </c>
       <c r="H173" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I173" s="13"/>
     </row>
     <row r="174" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D174" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="175" spans="3:9" x14ac:dyDescent="0.3">
       <c r="E175" s="22" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="176" spans="3:9" x14ac:dyDescent="0.3">
       <c r="E176" s="22" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="177" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E177" s="22" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="178" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E178" s="22" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="179" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E179" s="25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="180" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E180" s="25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="181" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E181" s="22" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="183" spans="3:5" x14ac:dyDescent="0.3">
       <c r="C183" s="52"/>
       <c r="D183" s="8" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="184" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E184" s="22" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="185" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E185" s="22" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="186" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E186" s="22" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="187" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E187" s="22" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="188" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E188" s="22" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="189" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E189" s="22" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="190" spans="3:5" x14ac:dyDescent="0.3">
       <c r="E190" s="22" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="192" spans="3:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="C192" s="51"/>
       <c r="D192" s="8" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="193" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E193" s="27" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="194" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E194" s="27" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="195" spans="5:5" x14ac:dyDescent="0.3">
@@ -6719,7 +6728,7 @@
   <sheetData>
     <row r="2" spans="2:4" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="5"/>
@@ -6735,22 +6744,22 @@
       <c r="B4" s="6"/>
       <c r="C4" s="12"/>
       <c r="D4" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C5" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="3:3" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C24" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="3:3" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C45" s="11" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -6773,7 +6782,7 @@
   <sheetData>
     <row r="2" spans="2:4" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="5"/>
@@ -6789,55 +6798,55 @@
       <c r="B4" s="6"/>
       <c r="C4" s="12"/>
       <c r="D4" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C5" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="3:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D17" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="3:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D18" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="3:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D19" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="3:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D20" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E20" s="9"/>
     </row>
     <row r="21" spans="3:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D21" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="3:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D22" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E22" s="9"/>
     </row>
     <row r="23" spans="3:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D23" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E23" s="9"/>
     </row>
     <row r="24" spans="3:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D24" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E24" s="9"/>
     </row>
@@ -6847,20 +6856,20 @@
     </row>
     <row r="26" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C26" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E26" s="9"/>
     </row>
     <row r="27" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C27" s="10"/>
       <c r="D27" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C28" s="10"/>
       <c r="D28" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
@@ -6932,90 +6941,90 @@
       <c r="C45" s="10"/>
       <c r="D45" s="8"/>
       <c r="E45" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="46" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C46" s="10"/>
       <c r="D46" s="8"/>
       <c r="E46" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="47" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C47" s="10"/>
       <c r="D47" s="8"/>
       <c r="E47" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C48" s="10"/>
       <c r="D48" s="8"/>
       <c r="E48" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C49" s="10"/>
       <c r="D49" s="8"/>
       <c r="E49" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C50" s="10"/>
       <c r="D50" s="8"/>
       <c r="E50" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C51" s="10"/>
       <c r="D51" s="8"/>
       <c r="E51" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C52" s="10"/>
       <c r="D52" s="8"/>
       <c r="E52" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C53" s="10"/>
       <c r="D53" s="8"/>
       <c r="E53" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C54" s="10"/>
       <c r="D54" s="8"/>
       <c r="E54" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C55" s="10"/>
       <c r="D55" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C56" s="10"/>
       <c r="D56" s="8"/>
       <c r="E56" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C57" s="10"/>
       <c r="D57" s="8"/>
       <c r="E57" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
@@ -7066,154 +7075,154 @@
       <c r="C69" s="10"/>
       <c r="D69" s="8"/>
       <c r="E69" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="70" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C70" s="10"/>
       <c r="D70" s="8"/>
       <c r="E70" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C71" s="10"/>
       <c r="D71" s="8"/>
       <c r="E71" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C72" s="10"/>
       <c r="D72" s="8"/>
       <c r="E72" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="73" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C73" s="10"/>
       <c r="D73" s="8"/>
       <c r="E73" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C74" s="10"/>
       <c r="D74" s="8"/>
       <c r="E74" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="75" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C75" s="10"/>
       <c r="D75" s="8"/>
       <c r="E75" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C76" s="10"/>
       <c r="D76" s="8"/>
       <c r="E76" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="77" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C77" s="10"/>
       <c r="D77" s="8"/>
       <c r="E77" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C78" s="10"/>
       <c r="D78" s="8"/>
       <c r="E78" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C79" s="10"/>
       <c r="D79" s="8"/>
       <c r="E79" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C80" s="10"/>
       <c r="D80" s="48"/>
       <c r="E80" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="81" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C81" s="10"/>
       <c r="D81" s="8"/>
       <c r="E81" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="82" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C82" s="10"/>
       <c r="D82" s="8"/>
       <c r="E82" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="83" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C83" s="10"/>
       <c r="D83" s="8"/>
       <c r="E83" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="84" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C84" s="10"/>
       <c r="D84" s="8"/>
       <c r="E84" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="85" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C85" s="10"/>
       <c r="D85" s="8"/>
       <c r="E85" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="86" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C86" s="10"/>
       <c r="D86" s="8"/>
       <c r="E86" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="87" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C87" s="10"/>
       <c r="D87" s="8"/>
       <c r="E87" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="88" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C88" s="10"/>
       <c r="D88" s="8"/>
       <c r="E88" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="89" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C89" s="10"/>
       <c r="D89" s="8"/>
       <c r="E89" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="90" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C90" s="10"/>
       <c r="D90" s="8"/>
       <c r="E90" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="91" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
@@ -7260,225 +7269,225 @@
       <c r="C101" s="10"/>
       <c r="D101" s="8"/>
       <c r="E101" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="102" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C102" s="10"/>
       <c r="D102" s="8"/>
       <c r="E102" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="103" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C103" s="10"/>
       <c r="D103" s="8"/>
       <c r="E103" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="104" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C104" s="10"/>
       <c r="D104" s="8"/>
       <c r="E104" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="105" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C105" s="10"/>
       <c r="D105" s="8"/>
       <c r="E105" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="106" spans="3:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C106" s="10"/>
       <c r="D106" s="8"/>
       <c r="E106" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="107" spans="3:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D107" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="108" spans="3:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D108" s="8"/>
       <c r="E108" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="109" spans="3:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D109" s="8"/>
       <c r="E109" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110" spans="3:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D110" s="8"/>
       <c r="E110" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="124" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E124" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="125" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E125" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="126" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E126" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="127" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E127" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="128" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E128" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="129" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E129" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="130" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E130" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="131" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E131" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="132" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E132" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="134" spans="5:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="E134" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="148" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E148" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="149" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E149" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="150" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E150" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="151" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E151" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="152" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E152" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="153" spans="5:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="E153" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="167" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E167" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="168" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E168" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="169" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E169" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="170" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E170" s="21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="171" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E171" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="172" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E172" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="173" spans="5:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="E173" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="188" spans="5:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="E188" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="206" spans="5:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="E206" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="219" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E219" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="220" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E220" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="221" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E221" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="222" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E222" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="223" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E223" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="224" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E224" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="225" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E225" s="22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="226" spans="5:5" x14ac:dyDescent="0.3">
@@ -7486,47 +7495,47 @@
     </row>
     <row r="228" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E228" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="229" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E229" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="230" spans="5:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="E230" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="243" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E243" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="244" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E244" s="24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="245" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E245" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="246" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E246" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="247" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E247" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="248" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E248" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="249" spans="5:5" x14ac:dyDescent="0.3">
@@ -7537,94 +7546,94 @@
     </row>
     <row r="260" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E260" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="284" spans="5:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="E284" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="299" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E299" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="300" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E300" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="301" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E301" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="302" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E302" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="303" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E303" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="304" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E304" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="305" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E305" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="306" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E306" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="307" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E307" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="309" spans="4:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D309" s="47"/>
       <c r="E309" s="8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="320" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E320" s="9" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="321" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E321" s="9" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="322" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E322" s="9" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="323" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E323" s="9" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="324" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E324" s="9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="326" spans="4:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D326" s="47"/>
       <c r="E326" s="8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="327" spans="4:5" x14ac:dyDescent="0.3">
@@ -7632,37 +7641,37 @@
     </row>
     <row r="338" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E338" s="9" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="339" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E339" s="9" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="340" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E340" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="341" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E341" s="9" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="342" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E342" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="343" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E343" s="9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="344" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E344" s="9" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="345" spans="4:5" x14ac:dyDescent="0.3">
@@ -7671,89 +7680,89 @@
     <row r="346" spans="4:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D346" s="47"/>
       <c r="E346" s="8" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="358" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E358" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="359" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E359" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="360" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E360" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="361" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E361" s="9" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="362" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E362" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="363" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E363" s="9" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="365" spans="4:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D365" s="51"/>
       <c r="E365" s="8" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="379" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E379" s="9" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="380" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E380" s="9" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="381" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E381" s="9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="382" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E382" s="54" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="383" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E383" s="9" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="384" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E384" s="54" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="385" spans="4:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D385" s="51"/>
       <c r="E385" s="8" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="386" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E386" s="9" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="406" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E406" s="9" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
   </sheetData>
@@ -7780,7 +7789,7 @@
   <sheetData>
     <row r="2" spans="2:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="5"/>
@@ -7796,57 +7805,57 @@
       <c r="B4" s="6"/>
       <c r="C4" s="12"/>
       <c r="D4" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C6" s="11" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D6" s="5"/>
       <c r="F6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C7" s="12"/>
       <c r="D7" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D8" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D9" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D10" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D11" s="44" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D12" s="44" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="D13" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C15" s="11" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D15" s="27"/>
       <c r="E15" s="22"/>
@@ -7854,21 +7863,21 @@
     <row r="16" spans="2:6" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C16" s="10"/>
       <c r="D16" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E16" s="22"/>
     </row>
     <row r="17" spans="3:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C17" s="10"/>
       <c r="D17" s="27" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E17" s="22"/>
     </row>
     <row r="18" spans="3:8" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C18" s="10"/>
       <c r="D18" s="27" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E18" s="22"/>
     </row>
@@ -7880,16 +7889,16 @@
         <v>24</v>
       </c>
       <c r="E19" s="42" t="s">
+        <v>300</v>
+      </c>
+      <c r="F19" s="42" t="s">
+        <v>241</v>
+      </c>
+      <c r="G19" s="42" t="s">
         <v>301</v>
       </c>
-      <c r="F19" s="42" t="s">
-        <v>242</v>
-      </c>
-      <c r="G19" s="42" t="s">
-        <v>302</v>
-      </c>
       <c r="H19" s="42" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="3:8" x14ac:dyDescent="0.3">
@@ -7897,16 +7906,16 @@
         <v>0</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F20" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H20" s="39"/>
     </row>
@@ -7915,16 +7924,16 @@
         <v>1</v>
       </c>
       <c r="D21" s="38" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F21" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H21" s="39"/>
     </row>
@@ -7933,16 +7942,16 @@
         <v>2</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F22" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H22" s="39"/>
     </row>
@@ -7951,16 +7960,16 @@
         <v>3</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F23" s="40">
         <v>1.9230769230769201E-2</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H23" s="39"/>
     </row>
@@ -7969,16 +7978,16 @@
         <v>4</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E24" s="39" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F24" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G24" s="39" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H24" s="39"/>
     </row>
@@ -7987,16 +7996,16 @@
         <v>5</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E25" s="39" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F25" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G25" s="39" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H25" s="39"/>
     </row>
@@ -8005,16 +8014,16 @@
         <v>6</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E26" s="39" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F26" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G26" s="39" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H26" s="39"/>
     </row>
@@ -8023,16 +8032,16 @@
         <v>7</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E27" s="39" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F27" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G27" s="39" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H27" s="39"/>
     </row>
@@ -8041,16 +8050,16 @@
         <v>8</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E28" s="39" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F28" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G28" s="39" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H28" s="39"/>
     </row>
@@ -8059,16 +8068,16 @@
         <v>9</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E29" s="39" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F29" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G29" s="39" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H29" s="39"/>
     </row>
@@ -8077,16 +8086,16 @@
         <v>10</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E30" s="39" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F30" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G30" s="39" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H30" s="39"/>
     </row>
@@ -8095,16 +8104,16 @@
         <v>11</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E31" s="39" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F31" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G31" s="39" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H31" s="39"/>
     </row>
@@ -8113,16 +8122,16 @@
         <v>12</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E32" s="39" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F32" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G32" s="39" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H32" s="39"/>
     </row>
@@ -8134,16 +8143,16 @@
         <v>13</v>
       </c>
       <c r="D33" s="38" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E33" s="39" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F33" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G33" s="39" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H33" s="39"/>
     </row>
@@ -8155,16 +8164,16 @@
         <v>14</v>
       </c>
       <c r="D34" s="38" t="s">
+        <v>341</v>
+      </c>
+      <c r="E34" s="39" t="s">
         <v>342</v>
-      </c>
-      <c r="E34" s="39" t="s">
-        <v>343</v>
       </c>
       <c r="F34" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G34" s="39" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H34" s="39"/>
     </row>
@@ -8176,16 +8185,16 @@
         <v>15</v>
       </c>
       <c r="D35" s="38" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E35" s="39" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F35" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G35" s="39" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H35" s="39"/>
     </row>
@@ -8197,16 +8206,16 @@
         <v>16</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E36" s="39" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F36" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G36" s="39" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H36" s="39"/>
     </row>
@@ -8218,16 +8227,16 @@
         <v>17</v>
       </c>
       <c r="D37" s="38" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E37" s="39" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F37" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G37" s="39" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H37" s="39"/>
     </row>
@@ -8239,16 +8248,16 @@
         <v>18</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E38" s="39" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F38" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G38" s="39" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H38" s="39"/>
     </row>
@@ -8260,16 +8269,16 @@
         <v>19</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E39" s="39" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F39" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G39" s="39" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H39" s="39"/>
     </row>
@@ -8281,16 +8290,16 @@
         <v>20</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E40" s="39" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F40" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G40" s="39" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H40" s="39"/>
     </row>
@@ -8302,16 +8311,16 @@
         <v>21</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E41" s="39" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F41" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G41" s="39" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H41" s="39"/>
     </row>
@@ -8323,16 +8332,16 @@
         <v>22</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E42" s="39" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F42" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G42" s="39" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H42" s="39"/>
     </row>
@@ -8344,16 +8353,16 @@
         <v>23</v>
       </c>
       <c r="D43" s="38" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E43" s="39" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F43" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G43" s="39" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H43" s="39"/>
     </row>
@@ -8365,100 +8374,100 @@
         <v>24</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E44" s="39" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F44" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G44" s="39" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H44" s="39"/>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C45" s="41">
         <v>25</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E45" s="39" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F45" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G45" s="39" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H45" s="39"/>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C46" s="41">
         <v>26</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E46" s="39" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F46" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G46" s="39" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H46" s="39"/>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C47" s="41">
         <v>27</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E47" s="39" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F47" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G47" s="39" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H47" s="39"/>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C48" s="41">
         <v>28</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E48" s="39" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F48" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G48" s="39" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H48" s="39"/>
     </row>
@@ -8473,16 +8482,16 @@
         <v>29</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E49" s="39" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F49" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G49" s="39" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H49" s="39"/>
     </row>
@@ -8497,16 +8506,16 @@
         <v>30</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E50" s="39" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F50" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G50" s="39" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H50" s="39"/>
     </row>
@@ -8521,16 +8530,16 @@
         <v>31</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E51" s="39" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F51" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G51" s="39" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H51" s="39"/>
     </row>
@@ -8545,16 +8554,16 @@
         <v>32</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E52" s="39" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F52" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G52" s="39" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H52" s="39"/>
     </row>
@@ -8569,16 +8578,16 @@
         <v>33</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E53" s="39" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F53" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G53" s="39" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H53" s="39"/>
     </row>
@@ -8590,16 +8599,16 @@
         <v>34</v>
       </c>
       <c r="D54" s="38" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E54" s="39" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F54" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G54" s="39" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H54" s="39"/>
     </row>
@@ -8611,16 +8620,16 @@
         <v>35</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E55" s="39" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F55" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G55" s="39" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H55" s="39"/>
     </row>
@@ -8632,16 +8641,16 @@
         <v>36</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E56" s="39" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F56" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G56" s="39" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H56" s="39"/>
     </row>
@@ -8653,16 +8662,16 @@
         <v>37</v>
       </c>
       <c r="D57" s="38" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E57" s="39" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F57" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G57" s="39" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H57" s="39"/>
     </row>
@@ -8674,16 +8683,16 @@
         <v>38</v>
       </c>
       <c r="D58" s="38" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E58" s="39" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F58" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G58" s="39" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H58" s="39"/>
     </row>
@@ -8692,16 +8701,16 @@
         <v>39</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E59" s="39" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F59" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G59" s="39" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H59" s="39"/>
     </row>
@@ -8710,16 +8719,16 @@
         <v>40</v>
       </c>
       <c r="D60" s="38" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E60" s="39" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F60" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G60" s="39" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H60" s="39"/>
     </row>
@@ -8728,16 +8737,16 @@
         <v>41</v>
       </c>
       <c r="D61" s="38" t="s">
+        <v>425</v>
+      </c>
+      <c r="E61" s="39" t="s">
         <v>426</v>
-      </c>
-      <c r="E61" s="39" t="s">
-        <v>427</v>
       </c>
       <c r="F61" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G61" s="39" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H61" s="39"/>
     </row>
@@ -8746,16 +8755,16 @@
         <v>42</v>
       </c>
       <c r="D62" s="38" t="s">
+        <v>428</v>
+      </c>
+      <c r="E62" s="39" t="s">
         <v>429</v>
-      </c>
-      <c r="E62" s="39" t="s">
-        <v>430</v>
       </c>
       <c r="F62" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G62" s="39" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H62" s="39"/>
     </row>
@@ -8767,16 +8776,16 @@
         <v>43</v>
       </c>
       <c r="D63" s="38" t="s">
+        <v>431</v>
+      </c>
+      <c r="E63" s="39" t="s">
         <v>432</v>
-      </c>
-      <c r="E63" s="39" t="s">
-        <v>433</v>
       </c>
       <c r="F63" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G63" s="39" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H63" s="39"/>
     </row>
@@ -8788,16 +8797,16 @@
         <v>44</v>
       </c>
       <c r="D64" s="38" t="s">
+        <v>434</v>
+      </c>
+      <c r="E64" s="39" t="s">
         <v>435</v>
-      </c>
-      <c r="E64" s="39" t="s">
-        <v>436</v>
       </c>
       <c r="F64" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G64" s="39" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H64" s="39"/>
     </row>
@@ -8809,16 +8818,16 @@
         <v>45</v>
       </c>
       <c r="D65" s="38" t="s">
+        <v>437</v>
+      </c>
+      <c r="E65" s="39" t="s">
         <v>438</v>
-      </c>
-      <c r="E65" s="39" t="s">
-        <v>439</v>
       </c>
       <c r="F65" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G65" s="39" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H65" s="39"/>
     </row>
@@ -8830,16 +8839,16 @@
         <v>46</v>
       </c>
       <c r="D66" s="38" t="s">
+        <v>440</v>
+      </c>
+      <c r="E66" s="39" t="s">
         <v>441</v>
-      </c>
-      <c r="E66" s="39" t="s">
-        <v>442</v>
       </c>
       <c r="F66" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G66" s="39" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H66" s="39"/>
     </row>
@@ -8851,16 +8860,16 @@
         <v>47</v>
       </c>
       <c r="D67" s="38" t="s">
+        <v>443</v>
+      </c>
+      <c r="E67" s="39" t="s">
         <v>444</v>
-      </c>
-      <c r="E67" s="39" t="s">
-        <v>445</v>
       </c>
       <c r="F67" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G67" s="39" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H67" s="39"/>
     </row>
@@ -8872,16 +8881,16 @@
         <v>48</v>
       </c>
       <c r="D68" s="38" t="s">
+        <v>446</v>
+      </c>
+      <c r="E68" s="39" t="s">
         <v>447</v>
-      </c>
-      <c r="E68" s="39" t="s">
-        <v>448</v>
       </c>
       <c r="F68" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G68" s="39" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H68" s="39"/>
     </row>
@@ -8893,16 +8902,16 @@
         <v>49</v>
       </c>
       <c r="D69" s="38" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E69" s="39" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F69" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G69" s="39" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H69" s="39"/>
     </row>
@@ -8914,16 +8923,16 @@
         <v>50</v>
       </c>
       <c r="D70" s="38" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E70" s="39" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F70" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G70" s="39" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H70" s="39"/>
     </row>
@@ -8935,16 +8944,16 @@
         <v>51</v>
       </c>
       <c r="D71" s="38" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E71" s="39" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F71" s="40">
         <v>1.9230769230769232E-2</v>
       </c>
       <c r="G71" s="39" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H71" s="39"/>
     </row>
@@ -8954,17 +8963,17 @@
         <v>1.0000000000000007</v>
       </c>
       <c r="G72" s="46" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="73" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D73" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="74" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D74" s="27" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.3">
@@ -8975,16 +8984,16 @@
         <v>24</v>
       </c>
       <c r="E75" s="42" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F75" s="42" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G75" s="42" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H75" s="42" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="76" spans="2:8" ht="27" x14ac:dyDescent="0.3">
@@ -8992,19 +9001,19 @@
         <v>0</v>
       </c>
       <c r="D76" s="39" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E76" s="39" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F76" s="39">
         <v>5</v>
       </c>
       <c r="G76" s="39" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H76" s="50" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.3">
@@ -9012,19 +9021,19 @@
         <v>1</v>
       </c>
       <c r="D77" s="39" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E77" s="39" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F77" s="39">
         <v>10</v>
       </c>
       <c r="G77" s="39" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H77" s="39" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.3">
@@ -9032,19 +9041,19 @@
         <v>2</v>
       </c>
       <c r="D78" s="39" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E78" s="39" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F78" s="39">
         <v>20</v>
       </c>
       <c r="G78" s="39" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H78" s="39" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.3">
@@ -9052,19 +9061,19 @@
         <v>3</v>
       </c>
       <c r="D79" s="39" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E79" s="39" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F79" s="39">
         <v>40</v>
       </c>
       <c r="G79" s="39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H79" s="39" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.3">
@@ -9072,19 +9081,19 @@
         <v>4</v>
       </c>
       <c r="D80" s="39" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E80" s="39" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F80" s="39">
         <v>200</v>
       </c>
       <c r="G80" s="39" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H80" s="39" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
@@ -9092,19 +9101,19 @@
         <v>5</v>
       </c>
       <c r="D81" s="39" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E81" s="39" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F81" s="39">
         <v>80</v>
       </c>
       <c r="G81" s="39" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H81" s="39" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
@@ -9112,19 +9121,19 @@
         <v>6</v>
       </c>
       <c r="D82" s="39" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E82" s="39" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F82" s="39">
         <v>100</v>
       </c>
       <c r="G82" s="39" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H82" s="39" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
@@ -9132,19 +9141,19 @@
         <v>7</v>
       </c>
       <c r="D83" s="39" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E83" s="39" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F83" s="39">
         <v>300</v>
       </c>
       <c r="G83" s="39" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H83" s="39" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
@@ -9152,19 +9161,19 @@
         <v>8</v>
       </c>
       <c r="D84" s="39" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E84" s="39" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F84" s="39">
         <v>500</v>
       </c>
       <c r="G84" s="39" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H84" s="39" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
@@ -9172,65 +9181,65 @@
         <v>9</v>
       </c>
       <c r="D85" s="39" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E85" s="39" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F85" s="39">
         <v>1000</v>
       </c>
       <c r="G85" s="39" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H85" s="39" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A87" s="51"/>
       <c r="D87" s="8" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D88" s="27" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D89" s="27" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D90" s="27" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D91" s="27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D92" s="27" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D93" s="27" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D94" s="27" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D95" s="27" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
@@ -9241,19 +9250,19 @@
         <v>24</v>
       </c>
       <c r="E96" s="42" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F96" s="42" t="s">
+        <v>559</v>
+      </c>
+      <c r="G96" s="42" t="s">
         <v>560</v>
       </c>
-      <c r="G96" s="42" t="s">
-        <v>561</v>
-      </c>
       <c r="H96" s="42" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I96" s="42" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -9262,22 +9271,22 @@
         <v>0</v>
       </c>
       <c r="D97" s="39" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E97" s="39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F97" s="39" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G97" s="53" t="s">
+        <v>571</v>
+      </c>
+      <c r="H97" s="53" t="s">
+        <v>568</v>
+      </c>
+      <c r="I97" s="49" t="s">
         <v>572</v>
-      </c>
-      <c r="H97" s="53" t="s">
-        <v>569</v>
-      </c>
-      <c r="I97" s="49" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -9285,22 +9294,22 @@
         <v>1</v>
       </c>
       <c r="D98" s="39" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E98" s="39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F98" s="39" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G98" s="53" t="s">
+        <v>573</v>
+      </c>
+      <c r="H98" s="53" t="s">
+        <v>569</v>
+      </c>
+      <c r="I98" s="50" t="s">
         <v>574</v>
-      </c>
-      <c r="H98" s="53" t="s">
-        <v>570</v>
-      </c>
-      <c r="I98" s="50" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -9308,22 +9317,22 @@
         <v>2</v>
       </c>
       <c r="D99" s="39" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E99" s="39" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F99" s="39" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G99" s="53" t="s">
+        <v>578</v>
+      </c>
+      <c r="H99" s="53" t="s">
+        <v>570</v>
+      </c>
+      <c r="I99" s="50" t="s">
         <v>579</v>
-      </c>
-      <c r="H99" s="53" t="s">
-        <v>571</v>
-      </c>
-      <c r="I99" s="50" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
@@ -9331,22 +9340,22 @@
         <v>3</v>
       </c>
       <c r="D100" s="39" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E100" s="39" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F100" s="39" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G100" s="53" t="s">
+        <v>575</v>
+      </c>
+      <c r="H100" s="53" t="s">
+        <v>567</v>
+      </c>
+      <c r="I100" s="53" t="s">
         <v>576</v>
-      </c>
-      <c r="H100" s="53" t="s">
-        <v>568</v>
-      </c>
-      <c r="I100" s="53" t="s">
-        <v>577</v>
       </c>
     </row>
   </sheetData>
@@ -9369,7 +9378,7 @@
   <sheetData>
     <row r="2" spans="2:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="5"/>
@@ -9385,12 +9394,12 @@
       <c r="B4" s="6"/>
       <c r="C4" s="12"/>
       <c r="D4" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="C6" s="11" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D6" s="5"/>
     </row>
@@ -9427,13 +9436,13 @@
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D15" s="9" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E15" s="25"/>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D16" s="9" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E16" s="25"/>
     </row>
@@ -9444,12 +9453,12 @@
     </row>
     <row r="18" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D18" s="22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="19" spans="3:8" x14ac:dyDescent="0.3">
       <c r="D19" s="22" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="20" spans="3:8" x14ac:dyDescent="0.3">
@@ -9488,7 +9497,7 @@
         <v>26</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H25" s="14" t="s">
         <v>27</v>
@@ -9506,7 +9515,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>37</v>
@@ -9521,10 +9530,10 @@
       </c>
       <c r="E27" s="58"/>
       <c r="F27" s="15" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>38</v>
@@ -9542,7 +9551,7 @@
         <v>36</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>39</v>
@@ -9560,7 +9569,7 @@
         <v>4</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H29" s="15" t="s">
         <v>42</v>
@@ -9578,7 +9587,7 @@
         <v>12</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H30" s="15" t="s">
         <v>43</v>
@@ -9596,7 +9605,7 @@
         <v>8</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H31" s="16" t="s">
         <v>41</v>
@@ -9614,26 +9623,26 @@
         <v>34</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H32" s="16" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="34" spans="4:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D34" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E34" s="22"/>
     </row>
     <row r="35" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D35" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D36" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="4:5" x14ac:dyDescent="0.3">
@@ -9674,79 +9683,79 @@
     </row>
     <row r="49" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D49" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D50" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J50" s="9"/>
     </row>
     <row r="51" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D51" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J51" s="9"/>
     </row>
     <row r="52" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D52" s="22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J52" s="9"/>
     </row>
     <row r="53" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D53" s="22" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J53" s="9"/>
     </row>
     <row r="54" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D54" s="22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J54" s="9"/>
     </row>
     <row r="55" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D55" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J55" s="22"/>
     </row>
     <row r="56" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D56" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J56" s="9"/>
     </row>
     <row r="57" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D57" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D58" s="22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="59" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D59" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D60" s="22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D61" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="62" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D62" s="17" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="63" spans="4:10" x14ac:dyDescent="0.3">
@@ -9757,7 +9766,7 @@
         <v>24</v>
       </c>
       <c r="F63" s="33" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G63" s="33" t="s">
         <v>27</v>
@@ -9768,13 +9777,13 @@
         <v>0</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="65" spans="4:7" x14ac:dyDescent="0.3">
@@ -9782,13 +9791,13 @@
         <v>1</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="66" spans="4:7" x14ac:dyDescent="0.3">
@@ -9796,13 +9805,13 @@
         <v>2</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="67" spans="4:7" x14ac:dyDescent="0.3">
@@ -9810,13 +9819,13 @@
         <v>3</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="68" spans="4:7" x14ac:dyDescent="0.3">
@@ -9824,18 +9833,18 @@
         <v>4</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="69" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D69" s="17" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="70" spans="4:7" x14ac:dyDescent="0.3">
@@ -9846,7 +9855,7 @@
         <v>24</v>
       </c>
       <c r="F70" s="33" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="71" spans="4:7" x14ac:dyDescent="0.3">
@@ -9873,7 +9882,7 @@
     </row>
     <row r="73" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D73" s="17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74" spans="4:7" x14ac:dyDescent="0.3">
@@ -9884,7 +9893,7 @@
         <v>24</v>
       </c>
       <c r="F74" s="33" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="75" spans="4:7" x14ac:dyDescent="0.3">
@@ -9892,7 +9901,7 @@
         <v>0</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F75" s="36">
         <v>0.6</v>
@@ -9903,7 +9912,7 @@
         <v>1</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F76" s="36">
         <v>0.3</v>
@@ -9914,7 +9923,7 @@
         <v>2</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F77" s="36">
         <v>0.1</v>
@@ -9922,7 +9931,7 @@
     </row>
     <row r="78" spans="4:7" x14ac:dyDescent="0.3">
       <c r="D78" s="17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="79" spans="4:7" x14ac:dyDescent="0.3">
@@ -9930,10 +9939,10 @@
         <v>23</v>
       </c>
       <c r="E79" s="33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F79" s="33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="80" spans="4:7" x14ac:dyDescent="0.3">
@@ -9947,18 +9956,18 @@
     </row>
     <row r="81" spans="4:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D81" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E81" s="25"/>
     </row>
     <row r="82" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D82" s="22" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="83" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D83" s="25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>

--- a/BoardGame_Excel/BoardGame_250703.xlsx
+++ b/BoardGame_Excel/BoardGame_250703.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="History" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="618">
   <si>
     <t>작성자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2111,69 +2111,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>같은 문양 카드 5장</t>
-  </si>
-  <si>
-    <t>문양이 같은 최고 숫자카드 5장</t>
-  </si>
-  <si>
     <t>25.06.28</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ex)All Spade | 9,10,11,12,13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ex) 9,10,11,12,13</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ex) All Spade | 5,6,7,8,9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>문양이 같고 숫자가 연속되는 카드 5장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ex) 3 Spade &amp; 2 Club</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ex) All Different Shape | 3,3,3,6,8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ex) All Different Shape | 4,4,4,4,6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ex) 3,3,4,4,7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ex) All Spade | 1,3,4,6,8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>카드 선택은 최소 1장에서 5장이다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2ㅂ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한 장만 선택할 시 적용 만약 조합에 맞는 카드가 없으면 솔로로 적용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>문양이 다른, 최고 또는 최소 숫자카드 4장</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2374,10 +2320,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>숫자가 같은 카드 3장과, 2장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2048 미니게임 시작
 최종 숫자만큼 데미지</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2389,6 +2331,124 @@
   </si>
   <si>
     <t>유저 체력 10% 회복</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>원페어</t>
+  </si>
+  <si>
+    <t>노페어</t>
+  </si>
+  <si>
+    <t>투페어</t>
+  </si>
+  <si>
+    <t>트리플</t>
+  </si>
+  <si>
+    <t>포카</t>
+  </si>
+  <si>
+    <t>플러쉬</t>
+  </si>
+  <si>
+    <t>풀하우스</t>
+  </si>
+  <si>
+    <t>스트레이트</t>
+  </si>
+  <si>
+    <t>백스트레이트</t>
+  </si>
+  <si>
+    <t>마운틴</t>
+  </si>
+  <si>
+    <t>헤르메스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아난케</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아틀라스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hermes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ananke</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Atlas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스트레이트 플러쉬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백 스트레이트 플러쉬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로얄 스트레이트 플러쉬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5장의 카드로 위의 경우 어디에도 해당하지 않는 패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5장의 카드 중에서 2장의 숫자가 같은 패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>같은 숫자 두 개(원페어)가 두 쌍이 있는 패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5장의 카드 중에서 3장의 숫자가 같은 패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 무늬가 같지는 않고 카드 5장의 숫자가 연달아 있는 패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 무늬가 같지는 않고 A, 2, 3, 4, 5가 연달아 있는 패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 무늬가 같지는 않고 10, J, Q, K, A가 연달아 있는 패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카드 5장 모두 무늬가 같은 패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>같은 숫자 3개(트리플)와 같은 숫자 2개(원페어)로 된 패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>같은 숫자의 카드 4장으로 되어 있는 패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카드 5장이 모두 무늬가 같으면서 숫자가 연달아 있는 패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카드 5장이 모두 무늬가 같으면서 A, 2, 3, 4, 5 연달아 있는 패</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카드 5장이 모두 무늬가 같으면서 10, J, Q, K, A 연달아 있는 패</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2606,7 +2666,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2655,13 +2715,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2844,6 +2913,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5081,10 +5159,10 @@
         <v>3</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D11" s="37" t="s">
-        <v>580</v>
+        <v>566</v>
       </c>
       <c r="O11" t="s">
         <v>297</v>
@@ -5101,10 +5179,10 @@
         <v>3</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
     </row>
     <row r="15" spans="2:83" x14ac:dyDescent="0.3">
@@ -5644,7 +5722,7 @@
         <v>481</v>
       </c>
       <c r="I78" s="15" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="J78" s="9"/>
     </row>
@@ -5682,7 +5760,7 @@
         <v>481</v>
       </c>
       <c r="I80" s="16" t="s">
-        <v>599</v>
+        <v>584</v>
       </c>
       <c r="J80" s="9"/>
     </row>
@@ -5701,7 +5779,7 @@
         <v>481</v>
       </c>
       <c r="I81" s="16" t="s">
-        <v>598</v>
+        <v>583</v>
       </c>
       <c r="J81" s="9"/>
     </row>
@@ -6670,17 +6748,17 @@
     <row r="192" spans="3:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="C192" s="51"/>
       <c r="D192" s="8" t="s">
-        <v>594</v>
+        <v>580</v>
       </c>
     </row>
     <row r="193" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E193" s="27" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
     </row>
     <row r="194" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E194" s="27" t="s">
-        <v>595</v>
+        <v>581</v>
       </c>
     </row>
     <row r="195" spans="5:5" x14ac:dyDescent="0.3">
@@ -7716,53 +7794,53 @@
     <row r="365" spans="4:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D365" s="51"/>
       <c r="E365" s="8" t="s">
-        <v>582</v>
+        <v>568</v>
       </c>
     </row>
     <row r="379" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E379" s="9" t="s">
-        <v>587</v>
+        <v>573</v>
       </c>
     </row>
     <row r="380" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E380" s="9" t="s">
-        <v>583</v>
+        <v>569</v>
       </c>
     </row>
     <row r="381" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E381" s="9" t="s">
-        <v>584</v>
+        <v>570</v>
       </c>
     </row>
     <row r="382" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E382" s="54" t="s">
-        <v>585</v>
+        <v>571</v>
       </c>
     </row>
     <row r="383" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E383" s="9" t="s">
-        <v>586</v>
+        <v>572</v>
       </c>
     </row>
     <row r="384" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E384" s="54" t="s">
-        <v>588</v>
+        <v>574</v>
       </c>
     </row>
     <row r="385" spans="4:5" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D385" s="51"/>
       <c r="E385" s="8" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
     </row>
     <row r="386" spans="4:5" x14ac:dyDescent="0.3">
       <c r="E386" s="9" t="s">
-        <v>590</v>
+        <v>576</v>
       </c>
     </row>
     <row r="406" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E406" s="9" t="s">
-        <v>591</v>
+        <v>577</v>
       </c>
     </row>
   </sheetData>
@@ -7777,13 +7855,14 @@
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A2:I100"/>
+  <dimension ref="A2:J103"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="3.625" customWidth="1"/>
     <col min="4" max="4" width="12.75" customWidth="1"/>
     <col min="6" max="6" width="10.75" customWidth="1"/>
-    <col min="7" max="8" width="39.375" customWidth="1"/>
+    <col min="7" max="7" width="52.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="39.375" customWidth="1"/>
     <col min="9" max="9" width="23.125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7814,7 +7893,7 @@
       </c>
       <c r="D6" s="5"/>
       <c r="F6" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="20.25" x14ac:dyDescent="0.3">
@@ -8389,7 +8468,7 @@
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="C45" s="41">
         <v>25</v>
@@ -8410,7 +8489,7 @@
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="C46" s="41">
         <v>26</v>
@@ -8431,7 +8510,7 @@
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="C47" s="41">
         <v>27</v>
@@ -8452,7 +8531,7 @@
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="C48" s="41">
         <v>28</v>
@@ -8810,7 +8889,7 @@
       </c>
       <c r="H64" s="39"/>
     </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>0</v>
       </c>
@@ -8831,7 +8910,7 @@
       </c>
       <c r="H65" s="39"/>
     </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>0</v>
       </c>
@@ -8852,7 +8931,7 @@
       </c>
       <c r="H66" s="39"/>
     </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>0</v>
       </c>
@@ -8873,7 +8952,7 @@
       </c>
       <c r="H67" s="39"/>
     </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>0</v>
       </c>
@@ -8894,7 +8973,7 @@
       </c>
       <c r="H68" s="39"/>
     </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>0</v>
       </c>
@@ -8915,7 +8994,7 @@
       </c>
       <c r="H69" s="39"/>
     </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>0</v>
       </c>
@@ -8936,7 +9015,7 @@
       </c>
       <c r="H70" s="39"/>
     </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>0</v>
       </c>
@@ -8957,7 +9036,7 @@
       </c>
       <c r="H71" s="39"/>
     </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.3">
       <c r="F72" s="45">
         <f>SUM(F20:F71)</f>
         <v>1.0000000000000007</v>
@@ -8966,17 +9045,17 @@
         <v>483</v>
       </c>
     </row>
-    <row r="73" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D73" s="8" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="74" spans="2:8" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D74" s="27" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C75" s="42" t="s">
         <v>23</v>
       </c>
@@ -8995,8 +9074,9 @@
       <c r="H75" s="42" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="76" spans="2:8" ht="27" x14ac:dyDescent="0.3">
+      <c r="J75" s="63"/>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C76" s="43">
         <v>0</v>
       </c>
@@ -9010,13 +9090,15 @@
         <v>5</v>
       </c>
       <c r="G76" s="39" t="s">
-        <v>200</v>
+        <v>605</v>
       </c>
       <c r="H76" s="50" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
+        <v>587</v>
+      </c>
+      <c r="I76" s="62"/>
+      <c r="J76" s="63"/>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C77" s="43">
         <v>1</v>
       </c>
@@ -9027,16 +9109,18 @@
         <v>465</v>
       </c>
       <c r="F77" s="39">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G77" s="39" t="s">
-        <v>201</v>
+        <v>606</v>
       </c>
       <c r="H77" s="39" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
+        <v>586</v>
+      </c>
+      <c r="I77" s="62"/>
+      <c r="J77" s="63"/>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C78" s="43">
         <v>2</v>
       </c>
@@ -9047,16 +9131,18 @@
         <v>466</v>
       </c>
       <c r="F78" s="39">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="G78" s="39" t="s">
-        <v>202</v>
+        <v>607</v>
       </c>
       <c r="H78" s="39" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
+        <v>588</v>
+      </c>
+      <c r="I78" s="62"/>
+      <c r="J78" s="63"/>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C79" s="43">
         <v>3</v>
       </c>
@@ -9067,295 +9153,365 @@
         <v>467</v>
       </c>
       <c r="F79" s="39">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="G79" s="39" t="s">
-        <v>204</v>
+        <v>608</v>
       </c>
       <c r="H79" s="39" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
+        <v>589</v>
+      </c>
+      <c r="I79" s="61"/>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
       <c r="C80" s="43">
         <v>4</v>
       </c>
       <c r="D80" s="39" t="s">
-        <v>194</v>
+        <v>596</v>
       </c>
       <c r="E80" s="39" t="s">
-        <v>468</v>
+        <v>599</v>
       </c>
       <c r="F80" s="39">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="G80" s="39" t="s">
-        <v>205</v>
+        <v>609</v>
       </c>
       <c r="H80" s="39" t="s">
-        <v>550</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="I80" s="61"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C81" s="43">
         <v>5</v>
       </c>
       <c r="D81" s="39" t="s">
-        <v>195</v>
+        <v>597</v>
       </c>
       <c r="E81" s="39" t="s">
-        <v>469</v>
+        <v>600</v>
       </c>
       <c r="F81" s="39">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="G81" s="39" t="s">
-        <v>541</v>
+        <v>610</v>
       </c>
       <c r="H81" s="39" t="s">
-        <v>552</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="I81" s="61"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C82" s="43">
         <v>6</v>
       </c>
       <c r="D82" s="39" t="s">
-        <v>196</v>
+        <v>598</v>
       </c>
       <c r="E82" s="39" t="s">
-        <v>470</v>
+        <v>601</v>
       </c>
       <c r="F82" s="39">
-        <v>100</v>
+        <v>360</v>
       </c>
       <c r="G82" s="39" t="s">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="H82" s="39" t="s">
-        <v>548</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="I82" s="61"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C83" s="43">
         <v>7</v>
       </c>
       <c r="D83" s="39" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E83" s="39" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F83" s="39">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="G83" s="39" t="s">
-        <v>547</v>
+        <v>612</v>
       </c>
       <c r="H83" s="39" t="s">
-        <v>546</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="I83" s="61"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C84" s="43">
         <v>8</v>
       </c>
       <c r="D84" s="39" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E84" s="39" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F84" s="39">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="G84" s="39" t="s">
-        <v>557</v>
+        <v>613</v>
       </c>
       <c r="H84" s="39" t="s">
-        <v>545</v>
-      </c>
+        <v>592</v>
+      </c>
+      <c r="I84" s="61"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C85" s="43">
         <v>9</v>
       </c>
       <c r="D85" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="E85" s="39" t="s">
+        <v>468</v>
+      </c>
+      <c r="F85" s="39">
+        <v>700</v>
+      </c>
+      <c r="G85" s="39" t="s">
+        <v>614</v>
+      </c>
+      <c r="H85" s="39" t="s">
+        <v>590</v>
+      </c>
+      <c r="I85" s="61"/>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C86" s="43">
+        <v>10</v>
+      </c>
+      <c r="D86" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="E86" s="39" t="s">
+        <v>471</v>
+      </c>
+      <c r="F86" s="39">
+        <v>860</v>
+      </c>
+      <c r="G86" s="39" t="s">
+        <v>615</v>
+      </c>
+      <c r="H86" s="39" t="s">
+        <v>602</v>
+      </c>
+      <c r="I86" s="61"/>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C87" s="43">
+        <v>11</v>
+      </c>
+      <c r="D87" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="E87" s="39" t="s">
+        <v>472</v>
+      </c>
+      <c r="F87" s="39">
+        <v>920</v>
+      </c>
+      <c r="G87" s="39" t="s">
+        <v>616</v>
+      </c>
+      <c r="H87" s="39" t="s">
+        <v>603</v>
+      </c>
+      <c r="I87" s="61"/>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C88" s="43">
+        <v>12</v>
+      </c>
+      <c r="D88" s="39" t="s">
         <v>199</v>
       </c>
-      <c r="E85" s="39" t="s">
+      <c r="E88" s="39" t="s">
         <v>473</v>
       </c>
-      <c r="F85" s="39">
+      <c r="F88" s="39">
         <v>1000</v>
       </c>
-      <c r="G85" s="39" t="s">
-        <v>542</v>
-      </c>
-      <c r="H85" s="39" t="s">
+      <c r="G88" s="39" t="s">
+        <v>617</v>
+      </c>
+      <c r="H88" s="39" t="s">
+        <v>604</v>
+      </c>
+      <c r="I88" s="61"/>
+    </row>
+    <row r="90" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A90" s="51"/>
+      <c r="D90" s="8" t="s">
         <v>544</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A87" s="51"/>
-      <c r="D87" s="8" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D88" s="27" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D89" s="27" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D90" s="27" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D91" s="27" t="s">
-        <v>562</v>
+        <v>547</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D92" s="27" t="s">
-        <v>563</v>
+        <v>578</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D93" s="27" t="s">
-        <v>564</v>
+        <v>579</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D94" s="27" t="s">
-        <v>565</v>
+        <v>548</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D95" s="27" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="C96" s="42" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D96" s="27" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D97" s="27" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D98" s="27" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C99" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="D96" s="42" t="s">
+      <c r="D99" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="E96" s="42" t="s">
+      <c r="E99" s="42" t="s">
         <v>300</v>
       </c>
-      <c r="F96" s="42" t="s">
+      <c r="F99" s="42" t="s">
+        <v>545</v>
+      </c>
+      <c r="G99" s="42" t="s">
+        <v>546</v>
+      </c>
+      <c r="H99" s="42" t="s">
+        <v>552</v>
+      </c>
+      <c r="I99" s="42" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="A100" s="47"/>
+      <c r="C100" s="43">
+        <v>0</v>
+      </c>
+      <c r="D100" s="39" t="s">
+        <v>529</v>
+      </c>
+      <c r="E100" s="39" t="s">
+        <v>533</v>
+      </c>
+      <c r="F100" s="39" t="s">
+        <v>537</v>
+      </c>
+      <c r="G100" s="53" t="s">
+        <v>557</v>
+      </c>
+      <c r="H100" s="53" t="s">
+        <v>554</v>
+      </c>
+      <c r="I100" s="49" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="C101" s="43">
+        <v>1</v>
+      </c>
+      <c r="D101" s="39" t="s">
+        <v>530</v>
+      </c>
+      <c r="E101" s="39" t="s">
+        <v>534</v>
+      </c>
+      <c r="F101" s="39" t="s">
+        <v>538</v>
+      </c>
+      <c r="G101" s="53" t="s">
         <v>559</v>
       </c>
-      <c r="G96" s="42" t="s">
+      <c r="H101" s="53" t="s">
+        <v>555</v>
+      </c>
+      <c r="I101" s="50" t="s">
         <v>560</v>
       </c>
-      <c r="H96" s="42" t="s">
-        <v>566</v>
-      </c>
-      <c r="I96" s="42" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="A97" s="47"/>
-      <c r="C97" s="43">
-        <v>0</v>
-      </c>
-      <c r="D97" s="39" t="s">
-        <v>529</v>
-      </c>
-      <c r="E97" s="39" t="s">
-        <v>533</v>
-      </c>
-      <c r="F97" s="39" t="s">
-        <v>537</v>
-      </c>
-      <c r="G97" s="53" t="s">
-        <v>571</v>
-      </c>
-      <c r="H97" s="53" t="s">
-        <v>568</v>
-      </c>
-      <c r="I97" s="49" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="C98" s="43">
-        <v>1</v>
-      </c>
-      <c r="D98" s="39" t="s">
-        <v>530</v>
-      </c>
-      <c r="E98" s="39" t="s">
-        <v>534</v>
-      </c>
-      <c r="F98" s="39" t="s">
-        <v>538</v>
-      </c>
-      <c r="G98" s="53" t="s">
-        <v>573</v>
-      </c>
-      <c r="H98" s="53" t="s">
-        <v>569</v>
-      </c>
-      <c r="I98" s="50" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="C99" s="43">
+    </row>
+    <row r="102" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="C102" s="43">
         <v>2</v>
       </c>
-      <c r="D99" s="39" t="s">
+      <c r="D102" s="39" t="s">
         <v>532</v>
       </c>
-      <c r="E99" s="39" t="s">
+      <c r="E102" s="39" t="s">
         <v>535</v>
       </c>
-      <c r="F99" s="39" t="s">
+      <c r="F102" s="39" t="s">
         <v>539</v>
       </c>
-      <c r="G99" s="53" t="s">
-        <v>578</v>
-      </c>
-      <c r="H99" s="53" t="s">
-        <v>570</v>
-      </c>
-      <c r="I99" s="50" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
-      <c r="C100" s="43">
+      <c r="G102" s="53" t="s">
+        <v>564</v>
+      </c>
+      <c r="H102" s="53" t="s">
+        <v>556</v>
+      </c>
+      <c r="I102" s="50" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="67.5" x14ac:dyDescent="0.3">
+      <c r="C103" s="43">
         <v>3</v>
       </c>
-      <c r="D100" s="39" t="s">
+      <c r="D103" s="39" t="s">
         <v>531</v>
       </c>
-      <c r="E100" s="39" t="s">
+      <c r="E103" s="39" t="s">
         <v>536</v>
       </c>
-      <c r="F100" s="39" t="s">
+      <c r="F103" s="39" t="s">
         <v>540</v>
       </c>
-      <c r="G100" s="53" t="s">
-        <v>575</v>
-      </c>
-      <c r="H100" s="53" t="s">
-        <v>567</v>
-      </c>
-      <c r="I100" s="53" t="s">
-        <v>576</v>
+      <c r="G103" s="53" t="s">
+        <v>561</v>
+      </c>
+      <c r="H103" s="53" t="s">
+        <v>553</v>
+      </c>
+      <c r="I103" s="53" t="s">
+        <v>562</v>
       </c>
     </row>
   </sheetData>
